--- a/data/trans_orig/DCD-Clase-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2012</t>
+          <t>Población con dolor crónico discapacitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23738</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46568</t>
+          <t>47993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40355</t>
+          <t>40178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70048</t>
+          <t>72288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405653</t>
+          <t>407072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425003</t>
+          <t>425279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267886</t>
+          <t>266461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290716</t>
+          <t>290689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681617</t>
+          <t>679377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711310</t>
+          <t>711487</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13611</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32922</t>
+          <t>33840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59128</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49953</t>
+          <t>51180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82762</t>
+          <t>84205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385875</t>
+          <t>384957</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405186</t>
+          <t>404829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278883</t>
+          <t>280662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>306291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674046</t>
+          <t>672603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706855</t>
+          <t>705628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39308</t>
+          <t>39288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71051</t>
+          <t>69291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24332</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>47246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70179</t>
+          <t>70084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108334</t>
+          <t>107023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558364</t>
+          <t>560124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>590107</t>
+          <t>590127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213532</t>
+          <t>212883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>235797</t>
+          <t>236573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>781210</t>
+          <t>782521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>819365</t>
+          <t>819460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78353</t>
+          <t>78340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116125</t>
+          <t>117479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86444</t>
+          <t>86985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125196</t>
+          <t>125670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174027</t>
+          <t>174973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231802</t>
+          <t>227649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1042884</t>
+          <t>1041530</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1080656</t>
+          <t>1080669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641461</t>
+          <t>640987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>680213</t>
+          <t>679672</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1693865</t>
+          <t>1698018</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1751640</t>
+          <t>1750694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24506</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46733</t>
+          <t>50198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136180</t>
+          <t>136780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181729</t>
+          <t>180668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167805</t>
+          <t>168326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>221021</t>
+          <t>218843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463863</t>
+          <t>460398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>486090</t>
+          <t>485558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>579793</t>
+          <t>580854</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>625342</t>
+          <t>624742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1051097</t>
+          <t>1053275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1104313</t>
+          <t>1103792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180352</t>
+          <t>178680</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>233047</t>
+          <t>231507</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181334</t>
+          <t>177311</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236276</t>
+          <t>232831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260205</t>
+          <t>259042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>876304</t>
+          <t>877844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>928999</t>
+          <t>930671</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1139957</t>
+          <t>1143402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1194899</t>
+          <t>1198922</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198444</t>
+          <t>200175</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>259923</t>
+          <t>260292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>536008</t>
+          <t>535823</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>628597</t>
+          <t>625889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>755491</t>
+          <t>754454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>866932</t>
+          <t>864860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3161987</t>
+          <t>3161618</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3223466</t>
+          <t>3221735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2921528</t>
+          <t>2924236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3014117</t>
+          <t>3014302</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6105103</t>
+          <t>6107175</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6216544</t>
+          <t>6217581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2016</t>
+          <t>Población con dolor crónico discapacitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36059</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37898</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66623</t>
+          <t>66783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393033</t>
+          <t>394087</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413432</t>
+          <t>413710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309000</t>
+          <t>308364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329192</t>
+          <t>329304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709524</t>
+          <t>709364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>738249</t>
+          <t>738087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>52246</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43543</t>
+          <t>42751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74226</t>
+          <t>74574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348682</t>
+          <t>348354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366702</t>
+          <t>367507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317267</t>
+          <t>320027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344359</t>
+          <t>344172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675274</t>
+          <t>674926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705957</t>
+          <t>706749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25931</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>49102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>22196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43401</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50877</t>
+          <t>52260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84931</t>
+          <t>84777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471878</t>
+          <t>472812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495983</t>
+          <t>495951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122722</t>
+          <t>124815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143945</t>
+          <t>143927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603105</t>
+          <t>603259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>637159</t>
+          <t>635776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69112</t>
+          <t>68063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106061</t>
+          <t>103066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76025</t>
+          <t>76381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114806</t>
+          <t>114750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155466</t>
+          <t>154812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205861</t>
+          <t>207544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1043577</t>
+          <t>1046572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1080526</t>
+          <t>1081575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711070</t>
+          <t>711126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>749851</t>
+          <t>749495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1769653</t>
+          <t>1767970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1820048</t>
+          <t>1820702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47986</t>
+          <t>48760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>79760</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106719</t>
+          <t>105871</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149242</t>
+          <t>147852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166362</t>
+          <t>165873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>220226</t>
+          <t>216278</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>540634</t>
+          <t>540946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>572720</t>
+          <t>571946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>589002</t>
+          <t>590392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>631525</t>
+          <t>632373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1138724</t>
+          <t>1142672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1192588</t>
+          <t>1193077</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117769</t>
+          <t>119108</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165178</t>
+          <t>165626</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122333</t>
+          <t>121595</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169072</t>
+          <t>166869</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279479</t>
+          <t>279422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>916847</t>
+          <t>916399</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>964256</t>
+          <t>962917</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1200098</t>
+          <t>1202301</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1246837</t>
+          <t>1247575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>200076</t>
+          <t>199073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>259002</t>
+          <t>260087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>419630</t>
+          <t>418350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>503882</t>
+          <t>502714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>636400</t>
+          <t>631739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>739175</t>
+          <t>736291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3126720</t>
+          <t>3125635</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3185646</t>
+          <t>3186649</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3027714</t>
+          <t>3028882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3111966</t>
+          <t>3113246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6178143</t>
+          <t>6181027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6280918</t>
+          <t>6285579</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante en 2023</t>
+          <t>Población con dolor crónico discapacitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32114</t>
+          <t>32479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56787</t>
+          <t>55786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74580</t>
+          <t>73655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103931</t>
+          <t>102760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111814</t>
+          <t>113737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150723</t>
+          <t>153448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448425</t>
+          <t>449426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>473098</t>
+          <t>472733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>343536</t>
+          <t>344707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>372887</t>
+          <t>373812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>801956</t>
+          <t>799231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>840865</t>
+          <t>838942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33541</t>
+          <t>35595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59642</t>
+          <t>59270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72729</t>
+          <t>74602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99682</t>
+          <t>101167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115041</t>
+          <t>114913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153481</t>
+          <t>151001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392571</t>
+          <t>392943</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418672</t>
+          <t>416618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>282898</t>
+          <t>281413</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>309851</t>
+          <t>307978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>681312</t>
+          <t>683792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>719752</t>
+          <t>719880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21910</t>
+          <t>23104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99626</t>
+          <t>101985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43487</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63749</t>
+          <t>62294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48343</t>
+          <t>53547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167789</t>
+          <t>165374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>568638</t>
+          <t>566279</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>646354</t>
+          <t>645160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103162</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123424</t>
+          <t>124331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667386</t>
+          <t>669801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>786832</t>
+          <t>781628</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147071</t>
+          <t>146414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192495</t>
+          <t>192810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96061</t>
+          <t>105533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241532</t>
+          <t>241080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249642</t>
+          <t>244469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>402716</t>
+          <t>401302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842324</t>
+          <t>842009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>887748</t>
+          <t>888405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>736562</t>
+          <t>737014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>882033</t>
+          <t>872561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1610196</t>
+          <t>1611610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1763270</t>
+          <t>1768443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71949</t>
+          <t>71662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105859</t>
+          <t>104223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187448</t>
+          <t>198052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298292</t>
+          <t>301446</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>281038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>384635</t>
+          <t>384430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369187</t>
+          <t>370823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403097</t>
+          <t>403384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>543043</t>
+          <t>539889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>653887</t>
+          <t>643283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>931746</t>
+          <t>931951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1030023</t>
+          <t>1035343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189105</t>
+          <t>189984</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>234273</t>
+          <t>231874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>192720</t>
+          <t>193656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242320</t>
+          <t>245066</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224593</t>
+          <t>224100</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237085</t>
+          <t>237166</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>527098</t>
+          <t>529497</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>572266</t>
+          <t>571387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>759558</t>
+          <t>756812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>809158</t>
+          <t>808222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>322815</t>
+          <t>328676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>460494</t>
+          <t>458494</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>711316</t>
+          <t>716090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>961918</t>
+          <t>960127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1135342</t>
+          <t>1129883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1401705</t>
+          <t>1397776</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2915566</t>
+          <t>2917566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3053245</t>
+          <t>3047384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2615840</t>
+          <t>2617631</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2866442</t>
+          <t>2861668</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5552113</t>
+          <t>5556042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5818476</t>
+          <t>5823935</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD-Clase-trans_orig.xlsx
+++ b/data/trans_orig/DCD-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>29539</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47993</t>
+          <t>48826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40178</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72288</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407072</t>
+          <t>407672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425279</t>
+          <t>424771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266461</t>
+          <t>265628</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290689</t>
+          <t>290254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>679377</t>
+          <t>682503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711487</t>
+          <t>711410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33840</t>
+          <t>33449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57349</t>
+          <t>59194</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51180</t>
+          <t>50493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>83164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384957</t>
+          <t>385348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404829</t>
+          <t>405437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280662</t>
+          <t>278817</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>306291</t>
+          <t>305875</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>672603</t>
+          <t>673644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705628</t>
+          <t>706315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39288</t>
+          <t>39432</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69291</t>
+          <t>68868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47246</t>
+          <t>47316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70084</t>
+          <t>71552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107023</t>
+          <t>108325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>560124</t>
+          <t>560547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>590127</t>
+          <t>589983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212883</t>
+          <t>212813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236573</t>
+          <t>235592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>782521</t>
+          <t>781219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>819460</t>
+          <t>817992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78340</t>
+          <t>78872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117479</t>
+          <t>121008</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86985</t>
+          <t>85936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125670</t>
+          <t>126059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174973</t>
+          <t>174210</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227649</t>
+          <t>231629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1041530</t>
+          <t>1038001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1080669</t>
+          <t>1080137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640987</t>
+          <t>640598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679672</t>
+          <t>680721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1698018</t>
+          <t>1694038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1750694</t>
+          <t>1751457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25038</t>
+          <t>24372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50198</t>
+          <t>48469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136780</t>
+          <t>134162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180668</t>
+          <t>178359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168326</t>
+          <t>166086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>218843</t>
+          <t>218028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>460398</t>
+          <t>462127</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485558</t>
+          <t>486224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>580854</t>
+          <t>583163</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>624742</t>
+          <t>627360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1053275</t>
+          <t>1054090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1103792</t>
+          <t>1106032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>178680</t>
+          <t>180554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>231507</t>
+          <t>234565</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>177311</t>
+          <t>178911</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232831</t>
+          <t>236405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259042</t>
+          <t>260175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>877844</t>
+          <t>874786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>930671</t>
+          <t>928797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1143402</t>
+          <t>1139828</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1198922</t>
+          <t>1197322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>200175</t>
+          <t>199671</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>260292</t>
+          <t>258744</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>535823</t>
+          <t>536077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>625889</t>
+          <t>626170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>754454</t>
+          <t>755859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>864860</t>
+          <t>868395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3161618</t>
+          <t>3163166</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3221735</t>
+          <t>3222239</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2924236</t>
+          <t>2923955</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3014302</t>
+          <t>3014048</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6107175</t>
+          <t>6103640</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6217581</t>
+          <t>6216176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>38637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38060</t>
+          <t>38090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66783</t>
+          <t>65614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>394087</t>
+          <t>394516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413710</t>
+          <t>413863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308364</t>
+          <t>308418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329304</t>
+          <t>328606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709364</t>
+          <t>710533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>738087</t>
+          <t>738057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>28126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28101</t>
+          <t>28156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52246</t>
+          <t>51243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42751</t>
+          <t>42547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>73179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348354</t>
+          <t>349101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367507</t>
+          <t>367488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320027</t>
+          <t>321030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344172</t>
+          <t>344117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674926</t>
+          <t>676321</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706749</t>
+          <t>706953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>25854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49102</t>
+          <t>49890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>22234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>43457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52260</t>
+          <t>52248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84777</t>
+          <t>85404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472812</t>
+          <t>472024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495951</t>
+          <t>496060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124815</t>
+          <t>122666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143927</t>
+          <t>143889</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603259</t>
+          <t>602632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635776</t>
+          <t>635788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68063</t>
+          <t>68340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103066</t>
+          <t>105326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76381</t>
+          <t>77515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114750</t>
+          <t>113598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154812</t>
+          <t>154274</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207544</t>
+          <t>208345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1046572</t>
+          <t>1044312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1081575</t>
+          <t>1081298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711126</t>
+          <t>712278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>749495</t>
+          <t>748361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1767970</t>
+          <t>1767169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1820702</t>
+          <t>1821240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48760</t>
+          <t>49480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79760</t>
+          <t>79554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105871</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147852</t>
+          <t>148092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165873</t>
+          <t>165460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216278</t>
+          <t>218233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>540946</t>
+          <t>541152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>571946</t>
+          <t>571226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>590392</t>
+          <t>590152</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632373</t>
+          <t>633042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1142672</t>
+          <t>1140717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1193077</t>
+          <t>1193490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119108</t>
+          <t>119233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165626</t>
+          <t>165334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121595</t>
+          <t>118502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>166869</t>
+          <t>168811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279422</t>
+          <t>279471</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>916399</t>
+          <t>916691</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>962917</t>
+          <t>962792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1202301</t>
+          <t>1200359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1247575</t>
+          <t>1250668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199073</t>
+          <t>199737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>260087</t>
+          <t>260646</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>418350</t>
+          <t>417236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>502714</t>
+          <t>504078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>631739</t>
+          <t>635020</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>736291</t>
+          <t>734972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3125635</t>
+          <t>3125076</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3186649</t>
+          <t>3185985</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3028882</t>
+          <t>3027518</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3113246</t>
+          <t>3114360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6181027</t>
+          <t>6182346</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6285579</t>
+          <t>6282298</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>47751</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32479</t>
+          <t>36334</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55786</t>
+          <t>61479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>88238</t>
+          <t>98792</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73655</t>
+          <t>82477</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102760</t>
+          <t>114632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>131598</t>
+          <t>146543</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113737</t>
+          <t>127276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153448</t>
+          <t>169005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>461851</t>
+          <t>502867</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449426</t>
+          <t>489139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472733</t>
+          <t>514284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>359229</t>
+          <t>389619</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>344707</t>
+          <t>373779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373812</t>
+          <t>405934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>821081</t>
+          <t>892486</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>799231</t>
+          <t>870024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>838942</t>
+          <t>911753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46556</t>
+          <t>47762</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35595</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59270</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86301</t>
+          <t>99507</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74602</t>
+          <t>85894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101167</t>
+          <t>116076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>132857</t>
+          <t>147269</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114913</t>
+          <t>128120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151001</t>
+          <t>167941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>405657</t>
+          <t>435450</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392943</t>
+          <t>421406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416618</t>
+          <t>447193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>296279</t>
+          <t>323636</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281413</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>307978</t>
+          <t>337249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>701936</t>
+          <t>759086</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683792</t>
+          <t>738414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>719880</t>
+          <t>778235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60063</t>
+          <t>66506</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>52318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101985</t>
+          <t>82896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53660</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42580</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62294</t>
+          <t>70918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>113723</t>
+          <t>126534</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53547</t>
+          <t>108172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165374</t>
+          <t>144832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>608201</t>
+          <t>405106</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>566279</t>
+          <t>388716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645160</t>
+          <t>419294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113251</t>
+          <t>127469</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104617</t>
+          <t>116579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>137042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>721452</t>
+          <t>532575</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669801</t>
+          <t>514277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>781628</t>
+          <t>550937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>168599</t>
+          <t>180975</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146414</t>
+          <t>158333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192810</t>
+          <t>206848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>183735</t>
+          <t>207582</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105533</t>
+          <t>186717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241080</t>
+          <t>229793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>352334</t>
+          <t>388557</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244469</t>
+          <t>356541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>401302</t>
+          <t>425338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>866220</t>
+          <t>950868</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842009</t>
+          <t>924995</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>888405</t>
+          <t>973510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>794359</t>
+          <t>653629</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>737014</t>
+          <t>631418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>872561</t>
+          <t>674494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1660578</t>
+          <t>1604497</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1611610</t>
+          <t>1567716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1768443</t>
+          <t>1636513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>87543</t>
+          <t>92544</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71662</t>
+          <t>76193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104223</t>
+          <t>111467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>260261</t>
+          <t>282701</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198052</t>
+          <t>260460</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>301446</t>
+          <t>306559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>347804</t>
+          <t>375245</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>281038</t>
+          <t>347145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>384430</t>
+          <t>406640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>387503</t>
+          <t>475420</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>370823</t>
+          <t>456497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403384</t>
+          <t>491771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>581074</t>
+          <t>548149</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>539889</t>
+          <t>524291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>643283</t>
+          <t>570390</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>968577</t>
+          <t>1023569</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>931951</t>
+          <t>992174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1035343</t>
+          <t>1051669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>209947</t>
+          <t>228618</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189984</t>
+          <t>206292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>231874</t>
+          <t>253580</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>217778</t>
+          <t>236165</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>193656</t>
+          <t>209213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>245066</t>
+          <t>263184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232676</t>
+          <t>229682</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224100</t>
+          <t>222237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237166</t>
+          <t>233957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>551424</t>
+          <t>615663</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>529497</t>
+          <t>590701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>571387</t>
+          <t>637989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>784100</t>
+          <t>845344</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>756812</t>
+          <t>818325</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>808222</t>
+          <t>872296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>413953</t>
+          <t>443085</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>328676</t>
+          <t>406705</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>458494</t>
+          <t>484150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>882142</t>
+          <t>977228</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>716090</t>
+          <t>933177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>960127</t>
+          <t>1023468</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1296094</t>
+          <t>1420313</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1129883</t>
+          <t>1363654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1397776</t>
+          <t>1484379</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2962107</t>
+          <t>2999391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2917566</t>
+          <t>2958326</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3047384</t>
+          <t>3035771</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2695616</t>
+          <t>2658165</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2617631</t>
+          <t>2611925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2861668</t>
+          <t>2702216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5657724</t>
+          <t>5657556</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5556042</t>
+          <t>5593490</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5823935</t>
+          <t>5714215</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
